--- a/docs/case_files/CASE_CLO.xlsx
+++ b/docs/case_files/CASE_CLO.xlsx
@@ -530,7 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -591,7 +590,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -635,7 +633,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -703,7 +700,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
@@ -783,7 +779,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
@@ -838,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO72"/>
+  <dimension ref="A1:AO86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1148,7 +1143,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K3" s="8" t="n"/>
+      <c r="K3" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" s="8" t="n"/>
       <c r="M3" s="8" t="n"/>
       <c r="N3" s="8" t="n"/>
@@ -1217,7 +1214,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K4" s="9" t="n"/>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
       <c r="N4" s="9" t="n"/>
@@ -1286,7 +1285,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K5" s="8" t="n"/>
+      <c r="K5" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="8" t="n"/>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n"/>
@@ -1355,7 +1356,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K6" s="9" t="n"/>
+      <c r="K6" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
       <c r="N6" s="9" t="n"/>
@@ -1424,7 +1427,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n"/>
+      <c r="K7" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
@@ -1493,7 +1498,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K8" s="9" t="n"/>
+      <c r="K8" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
       <c r="N8" s="9" t="n"/>
@@ -1562,7 +1569,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K9" s="8" t="n"/>
+      <c r="K9" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="8" t="n"/>
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8" t="n"/>
@@ -1631,7 +1640,9 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K10" s="9" t="n"/>
+      <c r="K10" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
@@ -1700,7 +1711,9 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K11" s="8" t="n"/>
+      <c r="K11" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="L11" s="8" t="n"/>
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n"/>
@@ -1769,7 +1782,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K12" s="9" t="n"/>
+      <c r="K12" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
       <c r="N12" s="9" t="n"/>
@@ -1838,7 +1853,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K13" s="8" t="n"/>
+      <c r="K13" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="8" t="n"/>
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n"/>
@@ -1907,7 +1924,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K14" s="9" t="n"/>
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
       <c r="N14" s="9" t="n"/>
@@ -1976,7 +1995,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K15" s="8" t="n"/>
+      <c r="K15" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="8" t="n"/>
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n"/>
@@ -2045,7 +2066,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K16" s="9" t="n"/>
+      <c r="K16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="9" t="n"/>
       <c r="N16" s="9" t="n"/>
@@ -2114,7 +2137,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K17" s="8" t="n"/>
+      <c r="K17" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" s="8" t="n"/>
       <c r="M17" s="8" t="n"/>
       <c r="N17" s="8" t="n"/>
@@ -2183,7 +2208,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K18" s="9" t="n"/>
+      <c r="K18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="9" t="n"/>
       <c r="N18" s="9" t="n"/>
@@ -2252,7 +2279,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K19" s="8" t="n"/>
+      <c r="K19" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="8" t="n"/>
       <c r="M19" s="8" t="n"/>
       <c r="N19" s="8" t="n"/>
@@ -2313,7 +2342,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K20" s="9" t="n"/>
+      <c r="K20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="9" t="n">
         <v>5401584.37788</v>
       </c>
@@ -2328,7 +2359,9 @@
       <c r="Q20" s="9" t="n">
         <v>1.4931</v>
       </c>
-      <c r="R20" s="9" t="n"/>
+      <c r="R20" s="9" t="n">
+        <v>1.0119</v>
+      </c>
       <c r="S20" s="9" t="n"/>
       <c r="T20" s="9" t="n"/>
       <c r="U20" s="9" t="n"/>
@@ -2380,7 +2413,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K21" s="8" t="n"/>
+      <c r="K21" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="8" t="n">
         <v>9907084.41633</v>
       </c>
@@ -2395,7 +2430,9 @@
       <c r="Q21" s="8" t="n">
         <v>1.2207</v>
       </c>
-      <c r="R21" s="8" t="n"/>
+      <c r="R21" s="8" t="n">
+        <v>1.2777</v>
+      </c>
       <c r="S21" s="8" t="n"/>
       <c r="T21" s="8" t="n"/>
       <c r="U21" s="8" t="n"/>
@@ -2447,7 +2484,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K22" s="9" t="n"/>
+      <c r="K22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="9" t="n">
         <v>10953959.84585344</v>
       </c>
@@ -2462,8 +2501,12 @@
       <c r="Q22" s="9" t="n">
         <v>1.2748</v>
       </c>
-      <c r="R22" s="9" t="n"/>
-      <c r="S22" s="9" t="n"/>
+      <c r="R22" s="9" t="n">
+        <v>1.1787</v>
+      </c>
+      <c r="S22" s="9" t="n">
+        <v>1.1422</v>
+      </c>
       <c r="T22" s="9" t="n"/>
       <c r="U22" s="9" t="n"/>
       <c r="V22" s="9" t="n"/>
@@ -2514,7 +2557,9 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K23" s="8" t="n"/>
+      <c r="K23" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="L23" s="8" t="n">
         <v>6027785.79971204</v>
       </c>
@@ -2529,11 +2574,19 @@
       <c r="Q23" s="8" t="n">
         <v>1.7601</v>
       </c>
-      <c r="R23" s="8" t="n"/>
-      <c r="S23" s="8" t="n"/>
+      <c r="R23" s="8" t="n">
+        <v>0.8332000000000001</v>
+      </c>
+      <c r="S23" s="8" t="n">
+        <v>1.0504</v>
+      </c>
       <c r="T23" s="8" t="n"/>
-      <c r="U23" s="8" t="n"/>
-      <c r="V23" s="8" t="n"/>
+      <c r="U23" s="8" t="n">
+        <v>3.9807</v>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v>26.2812</v>
+      </c>
       <c r="W23" s="8" t="n"/>
       <c r="X23" s="8" t="n"/>
       <c r="Y23" s="8" t="n"/>
@@ -2581,7 +2634,9 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K24" s="9" t="n"/>
+      <c r="K24" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="L24" s="9" t="n">
         <v>3951588.52383132</v>
       </c>
@@ -2596,11 +2651,19 @@
       <c r="Q24" s="9" t="n">
         <v>1.7716</v>
       </c>
-      <c r="R24" s="9" t="n"/>
-      <c r="S24" s="9" t="n"/>
+      <c r="R24" s="9" t="n">
+        <v>0.7326</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>0.8764999999999999</v>
+      </c>
       <c r="T24" s="9" t="n"/>
-      <c r="U24" s="9" t="n"/>
-      <c r="V24" s="9" t="n"/>
+      <c r="U24" s="9" t="n">
+        <v>5.719</v>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v>84.3862</v>
+      </c>
       <c r="W24" s="9" t="n"/>
       <c r="X24" s="9" t="n"/>
       <c r="Y24" s="9" t="n"/>
@@ -2648,7 +2711,9 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K25" s="8" t="n"/>
+      <c r="K25" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="8" t="n">
         <v>7780831.62784</v>
       </c>
@@ -2663,11 +2728,21 @@
       <c r="Q25" s="8" t="n">
         <v>1.7594</v>
       </c>
-      <c r="R25" s="8" t="n"/>
-      <c r="S25" s="8" t="n"/>
-      <c r="T25" s="8" t="n"/>
-      <c r="U25" s="8" t="n"/>
-      <c r="V25" s="8" t="n"/>
+      <c r="R25" s="8" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v>1.1784</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>3.7353</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>46.8714</v>
+      </c>
       <c r="W25" s="8" t="n"/>
       <c r="X25" s="8" t="n"/>
       <c r="Y25" s="8" t="n"/>
@@ -2715,7 +2790,9 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K26" s="9" t="n"/>
+      <c r="K26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="9" t="n">
         <v>5192039.1978</v>
       </c>
@@ -2730,11 +2807,21 @@
       <c r="Q26" s="9" t="n">
         <v>1.2769</v>
       </c>
-      <c r="R26" s="9" t="n"/>
-      <c r="S26" s="9" t="n"/>
-      <c r="T26" s="9" t="n"/>
-      <c r="U26" s="9" t="n"/>
-      <c r="V26" s="9" t="n"/>
+      <c r="R26" s="9" t="n">
+        <v>1.0319</v>
+      </c>
+      <c r="S26" s="9" t="n">
+        <v>0.8529</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V26" s="9" t="n">
+        <v>-16.5711</v>
+      </c>
       <c r="W26" s="9" t="n"/>
       <c r="X26" s="9" t="n"/>
       <c r="Y26" s="9" t="n"/>
@@ -2782,11 +2869,15 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K27" s="8" t="n"/>
+      <c r="K27" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="8" t="n">
         <v>8015796.67896</v>
       </c>
-      <c r="M27" s="8" t="n"/>
+      <c r="M27" s="8" t="n">
+        <v>1.0302</v>
+      </c>
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n">
         <v>1.386</v>
@@ -2797,11 +2888,21 @@
       <c r="Q27" s="8" t="n">
         <v>1.0004</v>
       </c>
-      <c r="R27" s="8" t="n"/>
-      <c r="S27" s="8" t="n"/>
-      <c r="T27" s="8" t="n"/>
-      <c r="U27" s="8" t="n"/>
-      <c r="V27" s="8" t="n"/>
+      <c r="R27" s="8" t="n">
+        <v>1.2381</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v>0.7848000000000001</v>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v>-5.9255</v>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v>-44.3339</v>
+      </c>
       <c r="W27" s="8" t="n"/>
       <c r="X27" s="8" t="n"/>
       <c r="Y27" s="8" t="n"/>
@@ -2849,11 +2950,15 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K28" s="9" t="n"/>
+      <c r="K28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" s="9" t="n">
         <v>8458909.49718</v>
       </c>
-      <c r="M28" s="9" t="n"/>
+      <c r="M28" s="9" t="n">
+        <v>1.0871</v>
+      </c>
       <c r="N28" s="9" t="n"/>
       <c r="O28" s="9" t="n">
         <v>1.3295</v>
@@ -2864,11 +2969,21 @@
       <c r="Q28" s="9" t="n">
         <v>1.3364</v>
       </c>
-      <c r="R28" s="9" t="n"/>
-      <c r="S28" s="9" t="n"/>
-      <c r="T28" s="9" t="n"/>
-      <c r="U28" s="9" t="n"/>
-      <c r="V28" s="9" t="n"/>
+      <c r="R28" s="9" t="n">
+        <v>0.9928</v>
+      </c>
+      <c r="S28" s="9" t="n">
+        <v>1.0763</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>-11.1831</v>
+      </c>
+      <c r="V28" s="9" t="n">
+        <v>-25.5172</v>
+      </c>
       <c r="W28" s="9" t="n"/>
       <c r="X28" s="9" t="n"/>
       <c r="Y28" s="9" t="n"/>
@@ -2916,11 +3031,15 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K29" s="8" t="n"/>
+      <c r="K29" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="L29" s="8" t="n">
         <v>5598056.12688</v>
       </c>
-      <c r="M29" s="8" t="n"/>
+      <c r="M29" s="8" t="n">
+        <v>0.7195</v>
+      </c>
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n">
         <v>1.4239</v>
@@ -2931,11 +3050,21 @@
       <c r="Q29" s="8" t="n">
         <v>1.3702</v>
       </c>
-      <c r="R29" s="8" t="n"/>
-      <c r="S29" s="8" t="n"/>
-      <c r="T29" s="8" t="n"/>
-      <c r="U29" s="8" t="n"/>
-      <c r="V29" s="8" t="n"/>
+      <c r="R29" s="8" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>1.0163</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>0.7734</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>-11.3277</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>3.7399</v>
+      </c>
       <c r="W29" s="8" t="n"/>
       <c r="X29" s="8" t="n"/>
       <c r="Y29" s="8" t="n"/>
@@ -2983,11 +3112,15 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K30" s="9" t="n"/>
+      <c r="K30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" s="9" t="n">
         <v>8242145.3114</v>
       </c>
-      <c r="M30" s="9" t="n"/>
+      <c r="M30" s="9" t="n">
+        <v>1.0593</v>
+      </c>
       <c r="N30" s="9" t="n"/>
       <c r="O30" s="9" t="n">
         <v>1.2965</v>
@@ -2998,11 +3131,21 @@
       <c r="Q30" s="9" t="n">
         <v>1.2978</v>
       </c>
-      <c r="R30" s="9" t="n"/>
-      <c r="S30" s="9" t="n"/>
-      <c r="T30" s="9" t="n"/>
-      <c r="U30" s="9" t="n"/>
-      <c r="V30" s="9" t="n"/>
+      <c r="R30" s="9" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="S30" s="9" t="n">
+        <v>0.9396</v>
+      </c>
+      <c r="T30" s="9" t="n">
+        <v>0.7376</v>
+      </c>
+      <c r="U30" s="9" t="n">
+        <v>-6.4574</v>
+      </c>
+      <c r="V30" s="9" t="n">
+        <v>21.197</v>
+      </c>
       <c r="W30" s="9" t="n"/>
       <c r="X30" s="9" t="n"/>
       <c r="Y30" s="9" t="n"/>
@@ -3050,11 +3193,15 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K31" s="8" t="n"/>
+      <c r="K31" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L31" s="8" t="n">
         <v>8558363.63646777</v>
       </c>
-      <c r="M31" s="8" t="n"/>
+      <c r="M31" s="8" t="n">
+        <v>1.0677</v>
+      </c>
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="n">
         <v>1.4351</v>
@@ -3065,11 +3212,21 @@
       <c r="Q31" s="8" t="n">
         <v>1.5504</v>
       </c>
-      <c r="R31" s="8" t="n"/>
-      <c r="S31" s="8" t="n"/>
-      <c r="T31" s="8" t="n"/>
-      <c r="U31" s="8" t="n"/>
-      <c r="V31" s="8" t="n"/>
+      <c r="R31" s="8" t="n">
+        <v>0.9018</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v>1.2142</v>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v>7.9428</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>18.8247</v>
+      </c>
       <c r="W31" s="8" t="n"/>
       <c r="X31" s="8" t="n"/>
       <c r="Y31" s="8" t="n"/>
@@ -3117,12 +3274,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K32" s="9" t="n"/>
+      <c r="K32" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="L32" s="9" t="n">
         <v>10723269.86372282</v>
       </c>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="9" t="n"/>
+      <c r="M32" s="9" t="n">
+        <v>1.3378</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>0.9671</v>
+      </c>
       <c r="O32" s="9" t="n">
         <v>1.369</v>
       </c>
@@ -3132,11 +3295,21 @@
       <c r="Q32" s="9" t="n">
         <v>1.2163</v>
       </c>
-      <c r="R32" s="9" t="n"/>
-      <c r="S32" s="9" t="n"/>
-      <c r="T32" s="9" t="n"/>
-      <c r="U32" s="9" t="n"/>
-      <c r="V32" s="9" t="n"/>
+      <c r="R32" s="9" t="n">
+        <v>1.2312</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>1.2158</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>-3.8556</v>
+      </c>
+      <c r="V32" s="9" t="n">
+        <v>-31.1261</v>
+      </c>
       <c r="W32" s="9" t="n"/>
       <c r="X32" s="9" t="n"/>
       <c r="Y32" s="9" t="n"/>
@@ -3184,12 +3357,18 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K33" s="8" t="n"/>
+      <c r="K33" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="8" t="n">
         <v>6511496.76942156</v>
       </c>
-      <c r="M33" s="8" t="n"/>
-      <c r="N33" s="8" t="n"/>
+      <c r="M33" s="8" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>0.3656</v>
+      </c>
       <c r="O33" s="8" t="n">
         <v>1.4242</v>
       </c>
@@ -3199,11 +3378,21 @@
       <c r="Q33" s="8" t="n">
         <v>1.661</v>
       </c>
-      <c r="R33" s="8" t="n"/>
-      <c r="S33" s="8" t="n"/>
-      <c r="T33" s="8" t="n"/>
-      <c r="U33" s="8" t="n"/>
-      <c r="V33" s="8" t="n"/>
+      <c r="R33" s="8" t="n">
+        <v>0.7784</v>
+      </c>
+      <c r="S33" s="8" t="n">
+        <v>0.9328</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>1.2429</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>9.849600000000001</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>34.8541</v>
+      </c>
       <c r="W33" s="8" t="n"/>
       <c r="X33" s="8" t="n"/>
       <c r="Y33" s="8" t="n"/>
@@ -3251,12 +3440,18 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K34" s="9" t="n"/>
+      <c r="K34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" s="9" t="n">
         <v>9314454.126250001</v>
       </c>
-      <c r="M34" s="9" t="n"/>
-      <c r="N34" s="9" t="n"/>
+      <c r="M34" s="9" t="n">
+        <v>1.1301</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>0.7659</v>
+      </c>
       <c r="O34" s="9" t="n">
         <v>1.2903</v>
       </c>
@@ -3266,11 +3461,21 @@
       <c r="Q34" s="9" t="n">
         <v>1.3952</v>
       </c>
-      <c r="R34" s="9" t="n"/>
-      <c r="S34" s="9" t="n"/>
-      <c r="T34" s="9" t="n"/>
-      <c r="U34" s="9" t="n"/>
-      <c r="V34" s="9" t="n"/>
+      <c r="R34" s="9" t="n">
+        <v>1.0216</v>
+      </c>
+      <c r="S34" s="9" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>1.0182</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>-10.0899</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>-20.6309</v>
+      </c>
       <c r="W34" s="9" t="n"/>
       <c r="X34" s="9" t="n"/>
       <c r="Y34" s="9" t="n"/>
@@ -3318,12 +3523,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K35" s="8" t="n"/>
+      <c r="K35" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="L35" s="8" t="n">
         <v>7799955.40226707</v>
       </c>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="8" t="n"/>
+      <c r="M35" s="8" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>0.5496</v>
+      </c>
       <c r="O35" s="8" t="n">
         <v>1.3699</v>
       </c>
@@ -3333,11 +3544,21 @@
       <c r="Q35" s="8" t="n">
         <v>1.9577</v>
       </c>
-      <c r="R35" s="8" t="n"/>
-      <c r="S35" s="8" t="n"/>
-      <c r="T35" s="8" t="n"/>
-      <c r="U35" s="8" t="n"/>
-      <c r="V35" s="8" t="n"/>
+      <c r="R35" s="8" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="S35" s="8" t="n">
+        <v>0.8042</v>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v>1.5085</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>0.06569999999999999</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>78.61320000000001</v>
+      </c>
       <c r="W35" s="8" t="n"/>
       <c r="X35" s="8" t="n"/>
       <c r="Y35" s="8" t="n"/>
@@ -3385,12 +3606,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K36" s="9" t="n"/>
+      <c r="K36" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="L36" s="9" t="n">
         <v>7521719.97990364</v>
       </c>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9" t="n"/>
+      <c r="M36" s="9" t="n">
+        <v>0.9643</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>0.5098</v>
+      </c>
       <c r="O36" s="9" t="n">
         <v>1.3659</v>
       </c>
@@ -3400,11 +3627,21 @@
       <c r="Q36" s="10" t="n">
         <v>2.2971</v>
       </c>
-      <c r="R36" s="9" t="n"/>
-      <c r="S36" s="9" t="n"/>
-      <c r="T36" s="9" t="n"/>
-      <c r="U36" s="9" t="n"/>
-      <c r="V36" s="9" t="n"/>
+      <c r="R36" s="9" t="n">
+        <v>0.6008</v>
+      </c>
+      <c r="S36" s="9" t="n">
+        <v>0.7291</v>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>1.4816</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>-4.0935</v>
+      </c>
+      <c r="V36" s="9" t="n">
+        <v>24.2444</v>
+      </c>
       <c r="W36" s="9" t="n"/>
       <c r="X36" s="9" t="n"/>
       <c r="Y36" s="9" t="n"/>
@@ -3452,12 +3689,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K37" s="8" t="n"/>
+      <c r="K37" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L37" s="8" t="n">
         <v>6279966.4326</v>
       </c>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="8" t="n"/>
+      <c r="M37" s="8" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="N37" s="8" t="n">
+        <v>0.3325</v>
+      </c>
       <c r="O37" s="8" t="n">
         <v>1.2475</v>
       </c>
@@ -3467,11 +3710,21 @@
       <c r="Q37" s="10" t="n">
         <v>2.059</v>
       </c>
-      <c r="R37" s="8" t="n"/>
-      <c r="S37" s="8" t="n"/>
-      <c r="T37" s="8" t="n"/>
-      <c r="U37" s="8" t="n"/>
-      <c r="V37" s="8" t="n"/>
+      <c r="R37" s="8" t="n">
+        <v>0.5968</v>
+      </c>
+      <c r="S37" s="8" t="n">
+        <v>0.6273</v>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v>1.6928</v>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v>-3.3171</v>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v>65.4949</v>
+      </c>
       <c r="W37" s="8" t="n"/>
       <c r="X37" s="8" t="n"/>
       <c r="Y37" s="8" t="n"/>
@@ -3519,12 +3772,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K38" s="9" t="n"/>
+      <c r="K38" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="L38" s="9" t="n">
         <v>5756863.8264714</v>
       </c>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="9" t="n"/>
+      <c r="M38" s="9" t="n">
+        <v>0.7381</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="O38" s="9" t="n">
         <v>1.2313</v>
       </c>
@@ -3534,11 +3793,21 @@
       <c r="Q38" s="9" t="n">
         <v>1.7345</v>
       </c>
-      <c r="R38" s="9" t="n"/>
-      <c r="S38" s="9" t="n"/>
-      <c r="T38" s="9" t="n"/>
-      <c r="U38" s="9" t="n"/>
-      <c r="V38" s="9" t="n"/>
+      <c r="R38" s="9" t="n">
+        <v>0.6753</v>
+      </c>
+      <c r="S38" s="9" t="n">
+        <v>0.6214</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>1.0443</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>-10.1175</v>
+      </c>
+      <c r="V38" s="9" t="n">
+        <v>-8.192299999999999</v>
+      </c>
       <c r="W38" s="9" t="n"/>
       <c r="X38" s="9" t="n"/>
       <c r="Y38" s="9" t="n"/>
@@ -3586,12 +3855,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K39" s="8" t="n"/>
+      <c r="K39" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="L39" s="8" t="n">
         <v>4022535.90598587</v>
       </c>
-      <c r="M39" s="8" t="n"/>
-      <c r="N39" s="8" t="n"/>
+      <c r="M39" s="8" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>0.0101</v>
+      </c>
       <c r="O39" s="8" t="n">
         <v>1.3211</v>
       </c>
@@ -3601,11 +3876,21 @@
       <c r="Q39" s="8" t="n">
         <v>1.1834</v>
       </c>
-      <c r="R39" s="8" t="n"/>
-      <c r="S39" s="8" t="n"/>
-      <c r="T39" s="8" t="n"/>
-      <c r="U39" s="8" t="n"/>
-      <c r="V39" s="8" t="n"/>
+      <c r="R39" s="8" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="S39" s="8" t="n">
+        <v>0.7208</v>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v>0.8482</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>-3.2799</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>-40.2411</v>
+      </c>
       <c r="W39" s="8" t="n"/>
       <c r="X39" s="8" t="n"/>
       <c r="Y39" s="8" t="n"/>
@@ -3653,12 +3938,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K40" s="9" t="n"/>
+      <c r="K40" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="L40" s="9" t="n">
         <v>4331632.83694946</v>
       </c>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9" t="n"/>
+      <c r="M40" s="9" t="n">
+        <v>0.5553</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>0.0543</v>
+      </c>
       <c r="O40" s="9" t="n">
         <v>1.094</v>
       </c>
@@ -3668,11 +3959,21 @@
       <c r="Q40" s="9" t="n">
         <v>1.03</v>
       </c>
-      <c r="R40" s="9" t="n"/>
-      <c r="S40" s="9" t="n"/>
-      <c r="T40" s="9" t="n"/>
-      <c r="U40" s="9" t="n"/>
-      <c r="V40" s="9" t="n"/>
+      <c r="R40" s="9" t="n">
+        <v>0.8915</v>
+      </c>
+      <c r="S40" s="9" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="T40" s="9" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="U40" s="9" t="n">
+        <v>-12.3046</v>
+      </c>
+      <c r="V40" s="9" t="n">
+        <v>-41.2879</v>
+      </c>
       <c r="W40" s="9" t="n"/>
       <c r="X40" s="9" t="n"/>
       <c r="Y40" s="9" t="n"/>
@@ -3720,12 +4021,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K41" s="8" t="n"/>
+      <c r="K41" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="8" t="n">
         <v>3929022.99509037</v>
       </c>
-      <c r="M41" s="8" t="n"/>
-      <c r="N41" s="8" t="n"/>
+      <c r="M41" s="8" t="n">
+        <v>0.5224</v>
+      </c>
+      <c r="N41" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" s="8" t="n">
         <v>1.0067</v>
       </c>
@@ -3735,11 +4042,21 @@
       <c r="Q41" s="8" t="n">
         <v>0.967</v>
       </c>
-      <c r="R41" s="8" t="n"/>
-      <c r="S41" s="8" t="n"/>
-      <c r="T41" s="8" t="n"/>
-      <c r="U41" s="8" t="n"/>
-      <c r="V41" s="8" t="n"/>
+      <c r="R41" s="8" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>0.8996</v>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>-18.2409</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>-33.209</v>
+      </c>
       <c r="W41" s="8" t="n"/>
       <c r="X41" s="8" t="n"/>
       <c r="Y41" s="8" t="n"/>
@@ -3787,12 +4104,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K42" s="9" t="n"/>
+      <c r="K42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="9" t="n">
         <v>4787827.4110047</v>
       </c>
-      <c r="M42" s="9" t="n"/>
-      <c r="N42" s="9" t="n"/>
+      <c r="M42" s="9" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>0.1223</v>
+      </c>
       <c r="O42" s="9" t="n">
         <v>1.0563</v>
       </c>
@@ -3802,11 +4125,21 @@
       <c r="Q42" s="9" t="n">
         <v>1.0593</v>
       </c>
-      <c r="R42" s="9" t="n"/>
-      <c r="S42" s="9" t="n"/>
-      <c r="T42" s="9" t="n"/>
-      <c r="U42" s="9" t="n"/>
-      <c r="V42" s="9" t="n"/>
+      <c r="R42" s="9" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="S42" s="9" t="n">
+        <v>0.8485</v>
+      </c>
+      <c r="T42" s="9" t="n">
+        <v>0.5145</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>-20.0439</v>
+      </c>
+      <c r="V42" s="9" t="n">
+        <v>-6.0876</v>
+      </c>
       <c r="W42" s="9" t="n"/>
       <c r="X42" s="9" t="n"/>
       <c r="Y42" s="9" t="n"/>
@@ -3854,12 +4187,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K43" s="8" t="n"/>
+      <c r="K43" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="8" t="n">
         <v>3981405.32652775</v>
       </c>
-      <c r="M43" s="8" t="n"/>
-      <c r="N43" s="8" t="n"/>
+      <c r="M43" s="8" t="n">
+        <v>0.6114000000000001</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>0.0075</v>
+      </c>
       <c r="O43" s="8" t="n">
         <v>1.0318</v>
       </c>
@@ -3869,11 +4208,21 @@
       <c r="Q43" s="8" t="n">
         <v>1.021</v>
       </c>
-      <c r="R43" s="8" t="n"/>
-      <c r="S43" s="8" t="n"/>
-      <c r="T43" s="8" t="n"/>
-      <c r="U43" s="8" t="n"/>
-      <c r="V43" s="8" t="n"/>
+      <c r="R43" s="8" t="n">
+        <v>0.7905</v>
+      </c>
+      <c r="S43" s="8" t="n">
+        <v>0.8147</v>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>-5.6856</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>6.3559</v>
+      </c>
       <c r="W43" s="8" t="n"/>
       <c r="X43" s="8" t="n"/>
       <c r="Y43" s="8" t="n"/>
@@ -3921,12 +4270,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K44" s="9" t="n"/>
+      <c r="K44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" s="9" t="n">
         <v>3876329.2152</v>
       </c>
-      <c r="M44" s="9" t="n"/>
-      <c r="N44" s="9" t="n"/>
+      <c r="M44" s="9" t="n">
+        <v>0.6173</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="O44" s="9" t="n">
         <v>1.0454</v>
       </c>
@@ -3936,11 +4291,21 @@
       <c r="Q44" s="9" t="n">
         <v>0.9406</v>
       </c>
-      <c r="R44" s="9" t="n"/>
-      <c r="S44" s="9" t="n"/>
-      <c r="T44" s="9" t="n"/>
-      <c r="U44" s="9" t="n"/>
-      <c r="V44" s="9" t="n"/>
+      <c r="R44" s="9" t="n">
+        <v>0.8584000000000001</v>
+      </c>
+      <c r="S44" s="9" t="n">
+        <v>0.8249</v>
+      </c>
+      <c r="T44" s="9" t="n">
+        <v>0.7948</v>
+      </c>
+      <c r="U44" s="9" t="n">
+        <v>3.8442</v>
+      </c>
+      <c r="V44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="W44" s="9" t="n"/>
       <c r="X44" s="9" t="n"/>
       <c r="Y44" s="9" t="n"/>
@@ -3988,12 +4353,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K45" s="8" t="n"/>
+      <c r="K45" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" s="8" t="n">
         <v>4060452.70568</v>
       </c>
-      <c r="M45" s="8" t="n"/>
-      <c r="N45" s="8" t="n"/>
+      <c r="M45" s="8" t="n">
+        <v>0.7053</v>
+      </c>
+      <c r="N45" s="8" t="n">
+        <v>0.026</v>
+      </c>
       <c r="O45" s="8" t="n">
         <v>1.1075</v>
       </c>
@@ -4003,11 +4374,21 @@
       <c r="Q45" s="8" t="n">
         <v>0.9893</v>
       </c>
-      <c r="R45" s="8" t="n"/>
-      <c r="S45" s="8" t="n"/>
-      <c r="T45" s="8" t="n"/>
-      <c r="U45" s="8" t="n"/>
-      <c r="V45" s="8" t="n"/>
+      <c r="R45" s="8" t="n">
+        <v>0.8705000000000001</v>
+      </c>
+      <c r="S45" s="8" t="n">
+        <v>0.8391</v>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v>4.8471</v>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v>-0.2822</v>
+      </c>
       <c r="W45" s="8" t="n"/>
       <c r="X45" s="8" t="n"/>
       <c r="Y45" s="8" t="n"/>
@@ -4055,12 +4436,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K46" s="9" t="n"/>
+      <c r="K46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="9" t="n">
         <v>4434766.97525783</v>
       </c>
-      <c r="M46" s="9" t="n"/>
-      <c r="N46" s="9" t="n"/>
+      <c r="M46" s="9" t="n">
+        <v>0.9263</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>0.0789</v>
+      </c>
       <c r="O46" s="9" t="n">
         <v>1.0897</v>
       </c>
@@ -4070,11 +4457,21 @@
       <c r="Q46" s="9" t="n">
         <v>0.9246</v>
       </c>
-      <c r="R46" s="9" t="n"/>
-      <c r="S46" s="9" t="n"/>
-      <c r="T46" s="9" t="n"/>
-      <c r="U46" s="9" t="n"/>
-      <c r="V46" s="9" t="n"/>
+      <c r="R46" s="9" t="n">
+        <v>0.9171</v>
+      </c>
+      <c r="S46" s="9" t="n">
+        <v>0.8816000000000001</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>0.9562</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>5.6116</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>-8.9641</v>
+      </c>
       <c r="W46" s="9" t="n"/>
       <c r="X46" s="9" t="n"/>
       <c r="Y46" s="9" t="n"/>
@@ -4122,12 +4519,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K47" s="8" t="n"/>
+      <c r="K47" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" s="8" t="n">
         <v>3942568.83741</v>
       </c>
-      <c r="M47" s="8" t="n"/>
-      <c r="N47" s="8" t="n"/>
+      <c r="M47" s="8" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="N47" s="8" t="n">
+        <v>0.0094</v>
+      </c>
       <c r="O47" s="8" t="n">
         <v>1.12</v>
       </c>
@@ -4137,11 +4540,21 @@
       <c r="Q47" s="8" t="n">
         <v>0.9223</v>
       </c>
-      <c r="R47" s="8" t="n"/>
-      <c r="S47" s="8" t="n"/>
-      <c r="T47" s="8" t="n"/>
-      <c r="U47" s="8" t="n"/>
-      <c r="V47" s="8" t="n"/>
+      <c r="R47" s="8" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="S47" s="8" t="n">
+        <v>0.9049</v>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v>0.8707</v>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v>7.136</v>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v>-1.0018</v>
+      </c>
       <c r="W47" s="8" t="n"/>
       <c r="X47" s="8" t="n"/>
       <c r="Y47" s="8" t="n"/>
@@ -4189,12 +4602,18 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K48" s="9" t="n"/>
+      <c r="K48" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" s="9" t="n">
         <v>3944340.43199352</v>
       </c>
-      <c r="M48" s="9" t="n"/>
-      <c r="N48" s="9" t="n"/>
+      <c r="M48" s="9" t="n">
+        <v>0.9106</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>0.009599999999999999</v>
+      </c>
       <c r="O48" s="9" t="n">
         <v>1.0139</v>
       </c>
@@ -4204,11 +4623,21 @@
       <c r="Q48" s="9" t="n">
         <v>0.9312</v>
       </c>
-      <c r="R48" s="9" t="n"/>
-      <c r="S48" s="9" t="n"/>
-      <c r="T48" s="9" t="n"/>
-      <c r="U48" s="9" t="n"/>
-      <c r="V48" s="9" t="n"/>
+      <c r="R48" s="9" t="n">
+        <v>0.8495</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>0.8986</v>
+      </c>
+      <c r="T48" s="9" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>-8.451499999999999</v>
+      </c>
+      <c r="V48" s="9" t="n">
+        <v>-6.1861</v>
+      </c>
       <c r="W48" s="9" t="n"/>
       <c r="X48" s="9" t="n"/>
       <c r="Y48" s="9" t="n"/>
@@ -4256,12 +4685,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K49" s="8" t="n"/>
+      <c r="K49" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L49" s="8" t="n">
         <v>6340872.81033777</v>
       </c>
-      <c r="M49" s="8" t="n"/>
-      <c r="N49" s="8" t="n"/>
+      <c r="M49" s="8" t="n">
+        <v>1.4639</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>0.3482</v>
+      </c>
       <c r="O49" s="8" t="n">
         <v>1.1237</v>
       </c>
@@ -4271,11 +4706,21 @@
       <c r="Q49" s="11" t="n">
         <v>0.8396</v>
       </c>
-      <c r="R49" s="8" t="n"/>
-      <c r="S49" s="8" t="n"/>
-      <c r="T49" s="8" t="n"/>
-      <c r="U49" s="8" t="n"/>
-      <c r="V49" s="8" t="n"/>
+      <c r="R49" s="8" t="n">
+        <v>1.255</v>
+      </c>
+      <c r="S49" s="8" t="n">
+        <v>0.9888</v>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v>0.8925999999999999</v>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v>3.1201</v>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v>-24.6423</v>
+      </c>
       <c r="W49" s="8" t="n"/>
       <c r="X49" s="8" t="n"/>
       <c r="Y49" s="8" t="n"/>
@@ -4323,12 +4768,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K50" s="9" t="n"/>
+      <c r="K50" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" s="9" t="n">
         <v>5445755.75201728</v>
       </c>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
+      <c r="M50" s="9" t="n">
+        <v>1.2572</v>
+      </c>
+      <c r="N50" s="9" t="n">
+        <v>0.2217</v>
+      </c>
       <c r="O50" s="9" t="n">
         <v>1.1371</v>
       </c>
@@ -4338,11 +4789,21 @@
       <c r="Q50" s="9" t="n">
         <v>1.4027</v>
       </c>
-      <c r="R50" s="9" t="n"/>
-      <c r="S50" s="9" t="n"/>
-      <c r="T50" s="9" t="n"/>
-      <c r="U50" s="9" t="n"/>
-      <c r="V50" s="9" t="n"/>
+      <c r="R50" s="9" t="n">
+        <v>0.8004</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="T50" s="9" t="n">
+        <v>1.4179</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>1.5268</v>
+      </c>
+      <c r="V50" s="9" t="n">
+        <v>17.8417</v>
+      </c>
       <c r="W50" s="9" t="n"/>
       <c r="X50" s="9" t="n"/>
       <c r="Y50" s="9" t="n"/>
@@ -4390,12 +4851,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K51" s="8" t="n"/>
+      <c r="K51" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L51" s="8" t="n">
         <v>5198573.02959624</v>
       </c>
-      <c r="M51" s="8" t="n"/>
-      <c r="N51" s="8" t="n"/>
+      <c r="M51" s="8" t="n">
+        <v>1.2001</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>0.1868</v>
+      </c>
       <c r="O51" s="8" t="n">
         <v>1.159</v>
       </c>
@@ -4405,11 +4872,21 @@
       <c r="Q51" s="8" t="n">
         <v>1.3793</v>
       </c>
-      <c r="R51" s="8" t="n"/>
-      <c r="S51" s="8" t="n"/>
-      <c r="T51" s="8" t="n"/>
-      <c r="U51" s="8" t="n"/>
-      <c r="V51" s="8" t="n"/>
+      <c r="R51" s="8" t="n">
+        <v>0.8421</v>
+      </c>
+      <c r="S51" s="8" t="n">
+        <v>0.9261</v>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v>1.4918</v>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v>14.3111</v>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v>15.3247</v>
+      </c>
       <c r="W51" s="8" t="n"/>
       <c r="X51" s="8" t="n"/>
       <c r="Y51" s="8" t="n"/>
@@ -4457,12 +4934,18 @@
           <t>HOT</t>
         </is>
       </c>
-      <c r="K52" s="9" t="n"/>
+      <c r="K52" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" s="9" t="n">
         <v>5661842.44683408</v>
       </c>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
+      <c r="M52" s="9" t="n">
+        <v>1.3071</v>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>0.2608</v>
+      </c>
       <c r="O52" s="9" t="n">
         <v>1.2752</v>
       </c>
@@ -4472,11 +4955,21 @@
       <c r="Q52" s="9" t="n">
         <v>1.6645</v>
       </c>
-      <c r="R52" s="9" t="n"/>
-      <c r="S52" s="9" t="n"/>
-      <c r="T52" s="9" t="n"/>
-      <c r="U52" s="9" t="n"/>
-      <c r="V52" s="9" t="n"/>
+      <c r="R52" s="9" t="n">
+        <v>0.7893</v>
+      </c>
+      <c r="S52" s="9" t="n">
+        <v>0.8093</v>
+      </c>
+      <c r="T52" s="9" t="n">
+        <v>1.8047</v>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>13.4822</v>
+      </c>
+      <c r="V52" s="9" t="n">
+        <v>80.44450000000001</v>
+      </c>
       <c r="W52" s="9" t="n"/>
       <c r="X52" s="9" t="n"/>
       <c r="Y52" s="9" t="n"/>
@@ -4524,12 +5017,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K53" s="8" t="n"/>
+      <c r="K53" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" s="8" t="n">
         <v>10162595.744</v>
       </c>
-      <c r="M53" s="8" t="n"/>
-      <c r="N53" s="8" t="n"/>
+      <c r="M53" s="8" t="n">
+        <v>2.2916</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>0.9181</v>
+      </c>
       <c r="O53" s="8" t="n">
         <v>1.1096</v>
       </c>
@@ -4539,11 +5038,21 @@
       <c r="Q53" s="11" t="n">
         <v>0.8488</v>
       </c>
-      <c r="R53" s="8" t="n"/>
-      <c r="S53" s="8" t="n"/>
-      <c r="T53" s="8" t="n"/>
-      <c r="U53" s="8" t="n"/>
-      <c r="V53" s="8" t="n"/>
+      <c r="R53" s="8" t="n">
+        <v>1.4454</v>
+      </c>
+      <c r="S53" s="8" t="n">
+        <v>0.9426</v>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v>0.9115</v>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v>-2.4184</v>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v>-45.9633</v>
+      </c>
       <c r="W53" s="8" t="n"/>
       <c r="X53" s="8" t="n"/>
       <c r="Y53" s="8" t="n"/>
@@ -4591,12 +5100,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K54" s="9" t="n"/>
+      <c r="K54" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="9" t="n">
         <v>10394286.84042</v>
       </c>
-      <c r="M54" s="9" t="n"/>
-      <c r="N54" s="9" t="n"/>
+      <c r="M54" s="9" t="n">
+        <v>2.171</v>
+      </c>
+      <c r="N54" s="9" t="n">
+        <v>0.952</v>
+      </c>
       <c r="O54" s="9" t="n">
         <v>0.9578</v>
       </c>
@@ -4606,11 +5121,21 @@
       <c r="Q54" s="9" t="n">
         <v>0.8979</v>
       </c>
-      <c r="R54" s="9" t="n"/>
-      <c r="S54" s="9" t="n"/>
-      <c r="T54" s="9" t="n"/>
-      <c r="U54" s="9" t="n"/>
-      <c r="V54" s="9" t="n"/>
+      <c r="R54" s="9" t="n">
+        <v>1.1858</v>
+      </c>
+      <c r="S54" s="9" t="n">
+        <v>1.0475</v>
+      </c>
+      <c r="T54" s="9" t="n">
+        <v>1.0694</v>
+      </c>
+      <c r="U54" s="9" t="n">
+        <v>-17.3598</v>
+      </c>
+      <c r="V54" s="9" t="n">
+        <v>-41.3179</v>
+      </c>
       <c r="W54" s="9" t="n"/>
       <c r="X54" s="9" t="n"/>
       <c r="Y54" s="9" t="n"/>
@@ -4658,12 +5183,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K55" s="8" t="n"/>
+      <c r="K55" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" s="8" t="n">
         <v>7514938.3473</v>
       </c>
-      <c r="M55" s="8" t="n"/>
-      <c r="N55" s="8" t="n"/>
+      <c r="M55" s="8" t="n">
+        <v>1.4456</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>0.5314</v>
+      </c>
       <c r="O55" s="8" t="n">
         <v>1.0243</v>
       </c>
@@ -4673,11 +5204,21 @@
       <c r="Q55" s="8" t="n">
         <v>1.2774</v>
       </c>
-      <c r="R55" s="8" t="n"/>
-      <c r="S55" s="8" t="n"/>
-      <c r="T55" s="8" t="n"/>
-      <c r="U55" s="8" t="n"/>
-      <c r="V55" s="8" t="n"/>
+      <c r="R55" s="8" t="n">
+        <v>0.8662</v>
+      </c>
+      <c r="S55" s="8" t="n">
+        <v>1.121</v>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v>0.9107</v>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v>-19.6753</v>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v>-26.8119</v>
+      </c>
       <c r="W55" s="8" t="n"/>
       <c r="X55" s="8" t="n"/>
       <c r="Y55" s="8" t="n"/>
@@ -4725,12 +5266,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K56" s="9" t="n"/>
+      <c r="K56" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" s="9" t="n">
         <v>6573688.1478615</v>
       </c>
-      <c r="M56" s="9" t="n"/>
-      <c r="N56" s="9" t="n"/>
+      <c r="M56" s="9" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>0.394</v>
+      </c>
       <c r="O56" s="9" t="n">
         <v>0.9153</v>
       </c>
@@ -4740,11 +5287,21 @@
       <c r="Q56" s="9" t="n">
         <v>1.2967</v>
       </c>
-      <c r="R56" s="9" t="n"/>
-      <c r="S56" s="9" t="n"/>
-      <c r="T56" s="9" t="n"/>
-      <c r="U56" s="9" t="n"/>
-      <c r="V56" s="9" t="n"/>
+      <c r="R56" s="9" t="n">
+        <v>0.7504</v>
+      </c>
+      <c r="S56" s="9" t="n">
+        <v>0.9026</v>
+      </c>
+      <c r="T56" s="9" t="n">
+        <v>0.9401</v>
+      </c>
+      <c r="U56" s="9" t="n">
+        <v>-17.5108</v>
+      </c>
+      <c r="V56" s="9" t="n">
+        <v>58.8902</v>
+      </c>
       <c r="W56" s="9" t="n"/>
       <c r="X56" s="9" t="n"/>
       <c r="Y56" s="9" t="n"/>
@@ -4792,12 +5349,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K57" s="8" t="n"/>
+      <c r="K57" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="L57" s="8" t="n">
         <v>6264722.486</v>
       </c>
-      <c r="M57" s="8" t="n"/>
-      <c r="N57" s="8" t="n"/>
+      <c r="M57" s="8" t="n">
+        <v>1.1065</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>0.3488</v>
+      </c>
       <c r="O57" s="8" t="n">
         <v>0.8736</v>
       </c>
@@ -4807,11 +5370,21 @@
       <c r="Q57" s="8" t="n">
         <v>1.1552</v>
       </c>
-      <c r="R57" s="8" t="n"/>
-      <c r="S57" s="8" t="n"/>
-      <c r="T57" s="8" t="n"/>
-      <c r="U57" s="8" t="n"/>
-      <c r="V57" s="8" t="n"/>
+      <c r="R57" s="8" t="n">
+        <v>0.7448</v>
+      </c>
+      <c r="S57" s="8" t="n">
+        <v>0.7868000000000001</v>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v>-8.791</v>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v>45.2272</v>
+      </c>
       <c r="W57" s="8" t="n"/>
       <c r="X57" s="8" t="n"/>
       <c r="Y57" s="8" t="n"/>
@@ -4859,12 +5432,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K58" s="9" t="n"/>
+      <c r="K58" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="9" t="n">
         <v>5292524.61115794</v>
       </c>
-      <c r="M58" s="9" t="n"/>
-      <c r="N58" s="9" t="n"/>
+      <c r="M58" s="9" t="n">
+        <v>0.9348</v>
+      </c>
+      <c r="N58" s="9" t="n">
+        <v>0.2068</v>
+      </c>
       <c r="O58" s="9" t="n">
         <v>0.8885999999999999</v>
       </c>
@@ -4874,11 +5453,21 @@
       <c r="Q58" s="9" t="n">
         <v>1.0833</v>
       </c>
-      <c r="R58" s="9" t="n"/>
-      <c r="S58" s="9" t="n"/>
-      <c r="T58" s="9" t="n"/>
-      <c r="U58" s="9" t="n"/>
-      <c r="V58" s="9" t="n"/>
+      <c r="R58" s="9" t="n">
+        <v>0.7133</v>
+      </c>
+      <c r="S58" s="9" t="n">
+        <v>0.7359</v>
+      </c>
+      <c r="T58" s="9" t="n">
+        <v>1.2763</v>
+      </c>
+      <c r="U58" s="9" t="n">
+        <v>-13.2481</v>
+      </c>
+      <c r="V58" s="9" t="n">
+        <v>5.3446</v>
+      </c>
       <c r="W58" s="9" t="n"/>
       <c r="X58" s="9" t="n"/>
       <c r="Y58" s="9" t="n"/>
@@ -4926,12 +5515,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K59" s="8" t="n"/>
+      <c r="K59" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="L59" s="8" t="n">
         <v>5328140.14163772</v>
       </c>
-      <c r="M59" s="8" t="n"/>
-      <c r="N59" s="8" t="n"/>
+      <c r="M59" s="8" t="n">
+        <v>0.9411</v>
+      </c>
+      <c r="N59" s="8" t="n">
+        <v>0.212</v>
+      </c>
       <c r="O59" s="8" t="n">
         <v>0.8682</v>
       </c>
@@ -4941,11 +5536,21 @@
       <c r="Q59" s="8" t="n">
         <v>1.1404</v>
       </c>
-      <c r="R59" s="8" t="n"/>
-      <c r="S59" s="8" t="n"/>
-      <c r="T59" s="8" t="n"/>
-      <c r="U59" s="8" t="n"/>
-      <c r="V59" s="8" t="n"/>
+      <c r="R59" s="8" t="n">
+        <v>0.6877</v>
+      </c>
+      <c r="S59" s="8" t="n">
+        <v>0.7146</v>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v>1.2701</v>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v>-5.1459</v>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v>3.4924</v>
+      </c>
       <c r="W59" s="8" t="n"/>
       <c r="X59" s="8" t="n"/>
       <c r="Y59" s="8" t="n"/>
@@ -4993,12 +5598,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K60" s="9" t="n"/>
+      <c r="K60" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="L60" s="9" t="n">
         <v>4599085.25927466</v>
       </c>
-      <c r="M60" s="9" t="n"/>
-      <c r="N60" s="9" t="n"/>
+      <c r="M60" s="9" t="n">
+        <v>0.8123</v>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>0.1056</v>
+      </c>
       <c r="O60" s="9" t="n">
         <v>0.8507</v>
       </c>
@@ -5008,11 +5619,21 @@
       <c r="Q60" s="9" t="n">
         <v>0.865</v>
       </c>
-      <c r="R60" s="9" t="n"/>
-      <c r="S60" s="9" t="n"/>
-      <c r="T60" s="9" t="n"/>
-      <c r="U60" s="9" t="n"/>
-      <c r="V60" s="9" t="n"/>
+      <c r="R60" s="9" t="n">
+        <v>0.8473000000000001</v>
+      </c>
+      <c r="S60" s="9" t="n">
+        <v>0.7423999999999999</v>
+      </c>
+      <c r="T60" s="9" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="U60" s="9" t="n">
+        <v>-2.6213</v>
+      </c>
+      <c r="V60" s="9" t="n">
+        <v>-14.4075</v>
+      </c>
       <c r="W60" s="9" t="n"/>
       <c r="X60" s="9" t="n"/>
       <c r="Y60" s="9" t="n"/>
@@ -5060,12 +5681,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K61" s="8" t="n"/>
+      <c r="K61" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="L61" s="8" t="n">
         <v>4371288.11964</v>
       </c>
-      <c r="M61" s="8" t="n"/>
-      <c r="N61" s="8" t="n"/>
+      <c r="M61" s="8" t="n">
+        <v>0.7721</v>
+      </c>
+      <c r="N61" s="8" t="n">
+        <v>0.0723</v>
+      </c>
       <c r="O61" s="8" t="n">
         <v>1.0021</v>
       </c>
@@ -5075,11 +5702,21 @@
       <c r="Q61" s="8" t="n">
         <v>0.8925</v>
       </c>
-      <c r="R61" s="8" t="n"/>
-      <c r="S61" s="8" t="n"/>
-      <c r="T61" s="8" t="n"/>
-      <c r="U61" s="8" t="n"/>
-      <c r="V61" s="8" t="n"/>
+      <c r="R61" s="8" t="n">
+        <v>0.9396</v>
+      </c>
+      <c r="S61" s="8" t="n">
+        <v>0.8164</v>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v>0.6883</v>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v>12.7729</v>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v>-14.3855</v>
+      </c>
       <c r="W61" s="8" t="n"/>
       <c r="X61" s="8" t="n"/>
       <c r="Y61" s="8" t="n"/>
@@ -5127,12 +5764,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K62" s="9" t="n"/>
+      <c r="K62" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="L62" s="9" t="n">
         <v>4197739.2058812</v>
       </c>
-      <c r="M62" s="9" t="n"/>
-      <c r="N62" s="9" t="n"/>
+      <c r="M62" s="9" t="n">
+        <v>0.7413999999999999</v>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>0.0493</v>
+      </c>
       <c r="O62" s="9" t="n">
         <v>0.9601</v>
       </c>
@@ -5142,11 +5785,21 @@
       <c r="Q62" s="11" t="n">
         <v>0.8232</v>
       </c>
-      <c r="R62" s="9" t="n"/>
-      <c r="S62" s="9" t="n"/>
-      <c r="T62" s="9" t="n"/>
-      <c r="U62" s="9" t="n"/>
-      <c r="V62" s="9" t="n"/>
+      <c r="R62" s="9" t="n">
+        <v>0.9456</v>
+      </c>
+      <c r="S62" s="9" t="n">
+        <v>0.9116</v>
+      </c>
+      <c r="T62" s="9" t="n">
+        <v>0.7126</v>
+      </c>
+      <c r="U62" s="9" t="n">
+        <v>10.5851</v>
+      </c>
+      <c r="V62" s="9" t="n">
+        <v>-19.5738</v>
+      </c>
       <c r="W62" s="9" t="n"/>
       <c r="X62" s="9" t="n"/>
       <c r="Y62" s="9" t="n"/>
@@ -5194,12 +5847,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K63" s="8" t="n"/>
+      <c r="K63" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="L63" s="8" t="n">
         <v>4083933.85118823</v>
       </c>
-      <c r="M63" s="8" t="n"/>
-      <c r="N63" s="8" t="n"/>
+      <c r="M63" s="8" t="n">
+        <v>0.7499</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>0.0319</v>
+      </c>
       <c r="O63" s="8" t="n">
         <v>0.9053</v>
       </c>
@@ -5209,11 +5868,21 @@
       <c r="Q63" s="8" t="n">
         <v>0.8657</v>
       </c>
-      <c r="R63" s="8" t="n"/>
-      <c r="S63" s="8" t="n"/>
-      <c r="T63" s="8" t="n"/>
-      <c r="U63" s="8" t="n"/>
-      <c r="V63" s="8" t="n"/>
+      <c r="R63" s="8" t="n">
+        <v>0.8165</v>
+      </c>
+      <c r="S63" s="8" t="n">
+        <v>0.8987000000000001</v>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v>0.7991</v>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v>6.4182</v>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v>10.4382</v>
+      </c>
       <c r="W63" s="8" t="n"/>
       <c r="X63" s="8" t="n"/>
       <c r="Y63" s="8" t="n"/>
@@ -5261,12 +5930,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K64" s="9" t="n"/>
+      <c r="K64" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="L64" s="9" t="n">
         <v>4049135.85531763</v>
       </c>
-      <c r="M64" s="9" t="n"/>
-      <c r="N64" s="9" t="n"/>
+      <c r="M64" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>0.0265</v>
+      </c>
       <c r="O64" s="9" t="n">
         <v>0.9093</v>
       </c>
@@ -5276,11 +5951,21 @@
       <c r="Q64" s="9" t="n">
         <v>0.9608</v>
       </c>
-      <c r="R64" s="9" t="n"/>
-      <c r="S64" s="9" t="n"/>
-      <c r="T64" s="9" t="n"/>
-      <c r="U64" s="9" t="n"/>
-      <c r="V64" s="9" t="n"/>
+      <c r="R64" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="S64" s="9" t="n">
+        <v>0.8356</v>
+      </c>
+      <c r="T64" s="9" t="n">
+        <v>0.8425</v>
+      </c>
+      <c r="U64" s="9" t="n">
+        <v>-9.2606</v>
+      </c>
+      <c r="V64" s="9" t="n">
+        <v>12.18</v>
+      </c>
       <c r="W64" s="9" t="n"/>
       <c r="X64" s="9" t="n"/>
       <c r="Y64" s="9" t="n"/>
@@ -5328,12 +6013,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K65" s="8" t="n"/>
+      <c r="K65" s="8" t="n">
+        <v>7</v>
+      </c>
       <c r="L65" s="8" t="n">
         <v>4365271.50135264</v>
       </c>
-      <c r="M65" s="8" t="n"/>
-      <c r="N65" s="8" t="n"/>
+      <c r="M65" s="8" t="n">
+        <v>0.8193</v>
+      </c>
+      <c r="N65" s="8" t="n">
+        <v>0.075</v>
+      </c>
       <c r="O65" s="8" t="n">
         <v>0.9209000000000001</v>
       </c>
@@ -5343,11 +6034,21 @@
       <c r="Q65" s="8" t="n">
         <v>1.1829</v>
       </c>
-      <c r="R65" s="8" t="n"/>
-      <c r="S65" s="8" t="n"/>
-      <c r="T65" s="8" t="n"/>
-      <c r="U65" s="8" t="n"/>
-      <c r="V65" s="8" t="n"/>
+      <c r="R65" s="8" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="S65" s="8" t="n">
+        <v>0.7164</v>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v>1.3675</v>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v>-4.0829</v>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v>49.0397</v>
+      </c>
       <c r="W65" s="8" t="n"/>
       <c r="X65" s="8" t="n"/>
       <c r="Y65" s="8" t="n"/>
@@ -5395,12 +6096,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K66" s="9" t="n"/>
+      <c r="K66" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="L66" s="9" t="n">
         <v>4347130.9404</v>
       </c>
-      <c r="M66" s="9" t="n"/>
-      <c r="N66" s="9" t="n"/>
+      <c r="M66" s="9" t="n">
+        <v>0.8214</v>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>0.0722</v>
+      </c>
       <c r="O66" s="9" t="n">
         <v>0.8989</v>
       </c>
@@ -5410,11 +6117,21 @@
       <c r="Q66" s="9" t="n">
         <v>1.2558</v>
       </c>
-      <c r="R66" s="9" t="n"/>
-      <c r="S66" s="9" t="n"/>
-      <c r="T66" s="9" t="n"/>
-      <c r="U66" s="9" t="n"/>
-      <c r="V66" s="9" t="n"/>
+      <c r="R66" s="9" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="S66" s="9" t="n">
+        <v>0.6292</v>
+      </c>
+      <c r="T66" s="9" t="n">
+        <v>1.4071</v>
+      </c>
+      <c r="U66" s="9" t="n">
+        <v>-0.7069</v>
+      </c>
+      <c r="V66" s="9" t="n">
+        <v>46.8344</v>
+      </c>
       <c r="W66" s="9" t="n"/>
       <c r="X66" s="9" t="n"/>
       <c r="Y66" s="9" t="n"/>
@@ -5462,12 +6179,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K67" s="8" t="n"/>
+      <c r="K67" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L67" s="8" t="n">
         <v>4171569.60738</v>
       </c>
-      <c r="M67" s="8" t="n"/>
-      <c r="N67" s="8" t="n"/>
+      <c r="M67" s="8" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="N67" s="8" t="n">
+        <v>0.0453</v>
+      </c>
       <c r="O67" s="8" t="n">
         <v>0.8699</v>
       </c>
@@ -5477,11 +6200,21 @@
       <c r="Q67" s="8" t="n">
         <v>1.401</v>
       </c>
-      <c r="R67" s="8" t="n"/>
-      <c r="S67" s="8" t="n"/>
-      <c r="T67" s="8" t="n"/>
-      <c r="U67" s="8" t="n"/>
-      <c r="V67" s="8" t="n"/>
+      <c r="R67" s="8" t="n">
+        <v>0.5102</v>
+      </c>
+      <c r="S67" s="8" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="T67" s="8" t="n">
+        <v>1.7019</v>
+      </c>
+      <c r="U67" s="8" t="n">
+        <v>-4.333</v>
+      </c>
+      <c r="V67" s="8" t="n">
+        <v>42.5025</v>
+      </c>
       <c r="W67" s="8" t="n"/>
       <c r="X67" s="8" t="n"/>
       <c r="Y67" s="8" t="n"/>
@@ -5529,12 +6262,18 @@
           <t>PINNED</t>
         </is>
       </c>
-      <c r="K68" s="9" t="n"/>
+      <c r="K68" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="L68" s="9" t="n">
         <v>4281205.78221041</v>
       </c>
-      <c r="M68" s="9" t="n"/>
-      <c r="N68" s="9" t="n"/>
+      <c r="M68" s="9" t="n">
+        <v>0.9794</v>
+      </c>
+      <c r="N68" s="9" t="n">
+        <v>0.0621</v>
+      </c>
       <c r="O68" s="9" t="n">
         <v>0.9161</v>
       </c>
@@ -5544,11 +6283,21 @@
       <c r="Q68" s="9" t="n">
         <v>1.4149</v>
       </c>
-      <c r="R68" s="9" t="n"/>
-      <c r="S68" s="9" t="n"/>
-      <c r="T68" s="9" t="n"/>
-      <c r="U68" s="9" t="n"/>
-      <c r="V68" s="9" t="n"/>
+      <c r="R68" s="9" t="n">
+        <v>0.5677</v>
+      </c>
+      <c r="S68" s="9" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="T68" s="9" t="n">
+        <v>1.6344</v>
+      </c>
+      <c r="U68" s="9" t="n">
+        <v>-0.5212</v>
+      </c>
+      <c r="V68" s="9" t="n">
+        <v>6.6416</v>
+      </c>
       <c r="W68" s="9" t="n"/>
       <c r="X68" s="9" t="n"/>
       <c r="Y68" s="9" t="n"/>
@@ -5596,12 +6345,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K69" s="8" t="n"/>
+      <c r="K69" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="8" t="n">
         <v>4174608.72</v>
       </c>
-      <c r="M69" s="8" t="n"/>
-      <c r="N69" s="8" t="n"/>
+      <c r="M69" s="8" t="n">
+        <v>0.9563</v>
+      </c>
+      <c r="N69" s="8" t="n">
+        <v>0.0458</v>
+      </c>
       <c r="O69" s="8" t="n">
         <v>0.9124</v>
       </c>
@@ -5611,11 +6366,21 @@
       <c r="Q69" s="8" t="n">
         <v>1.6738</v>
       </c>
-      <c r="R69" s="8" t="n"/>
-      <c r="S69" s="8" t="n"/>
-      <c r="T69" s="8" t="n"/>
-      <c r="U69" s="8" t="n"/>
-      <c r="V69" s="8" t="n"/>
+      <c r="R69" s="8" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="S69" s="8" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="T69" s="8" t="n">
+        <v>1.7421</v>
+      </c>
+      <c r="U69" s="8" t="n">
+        <v>1.5018</v>
+      </c>
+      <c r="V69" s="8" t="n">
+        <v>21.1658</v>
+      </c>
       <c r="W69" s="8" t="n"/>
       <c r="X69" s="8" t="n"/>
       <c r="Y69" s="8" t="n"/>
@@ -5663,12 +6428,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K70" s="9" t="n"/>
+      <c r="K70" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L70" s="9" t="n">
         <v>4177200.37314722</v>
       </c>
-      <c r="M70" s="9" t="n"/>
-      <c r="N70" s="9" t="n"/>
+      <c r="M70" s="9" t="n">
+        <v>0.9609</v>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>0.0462</v>
+      </c>
       <c r="O70" s="9" t="n">
         <v>0.9205</v>
       </c>
@@ -5678,11 +6449,21 @@
       <c r="Q70" s="9" t="n">
         <v>1.9612</v>
       </c>
-      <c r="R70" s="9" t="n"/>
-      <c r="S70" s="9" t="n"/>
-      <c r="T70" s="9" t="n"/>
-      <c r="U70" s="9" t="n"/>
-      <c r="V70" s="9" t="n"/>
+      <c r="R70" s="9" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="S70" s="9" t="n">
+        <v>0.4595</v>
+      </c>
+      <c r="T70" s="9" t="n">
+        <v>1.658</v>
+      </c>
+      <c r="U70" s="9" t="n">
+        <v>5.8168</v>
+      </c>
+      <c r="V70" s="9" t="n">
+        <v>40.5126</v>
+      </c>
       <c r="W70" s="9" t="n"/>
       <c r="X70" s="9" t="n"/>
       <c r="Y70" s="9" t="n"/>
@@ -5730,12 +6511,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K71" s="8" t="n"/>
+      <c r="K71" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" s="8" t="n">
         <v>4440584.6641422</v>
       </c>
-      <c r="M71" s="8" t="n"/>
-      <c r="N71" s="8" t="n"/>
+      <c r="M71" s="8" t="n">
+        <v>1.0215</v>
+      </c>
+      <c r="N71" s="8" t="n">
+        <v>0.0866</v>
+      </c>
       <c r="O71" s="8" t="n">
         <v>0.8831</v>
       </c>
@@ -5745,11 +6532,21 @@
       <c r="Q71" s="10" t="n">
         <v>2.2949</v>
       </c>
-      <c r="R71" s="8" t="n"/>
-      <c r="S71" s="8" t="n"/>
-      <c r="T71" s="8" t="n"/>
-      <c r="U71" s="8" t="n"/>
-      <c r="V71" s="8" t="n"/>
+      <c r="R71" s="8" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="S71" s="8" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v>1.8274</v>
+      </c>
+      <c r="U71" s="8" t="n">
+        <v>-3.6022</v>
+      </c>
+      <c r="V71" s="8" t="n">
+        <v>65.0245</v>
+      </c>
       <c r="W71" s="8" t="n"/>
       <c r="X71" s="8" t="n"/>
       <c r="Y71" s="8" t="n"/>
@@ -5797,12 +6594,18 @@
           <t>WARM</t>
         </is>
       </c>
-      <c r="K72" s="9" t="n"/>
+      <c r="K72" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="L72" s="9" t="n">
         <v>4632725.52288</v>
       </c>
-      <c r="M72" s="9" t="n"/>
-      <c r="N72" s="9" t="n"/>
+      <c r="M72" s="9" t="n">
+        <v>1.0657</v>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>0.116</v>
+      </c>
       <c r="O72" s="9" t="n">
         <v>0.8544</v>
       </c>
@@ -5812,11 +6615,21 @@
       <c r="Q72" s="10" t="n">
         <v>2.6483</v>
       </c>
-      <c r="R72" s="9" t="n"/>
-      <c r="S72" s="9" t="n"/>
-      <c r="T72" s="9" t="n"/>
-      <c r="U72" s="9" t="n"/>
-      <c r="V72" s="9" t="n"/>
+      <c r="R72" s="9" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="S72" s="9" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="T72" s="9" t="n">
+        <v>1.8903</v>
+      </c>
+      <c r="U72" s="9" t="n">
+        <v>-6.3569</v>
+      </c>
+      <c r="V72" s="9" t="n">
+        <v>46.7076</v>
+      </c>
       <c r="W72" s="9" t="n"/>
       <c r="X72" s="9" t="n"/>
       <c r="Y72" s="9" t="n"/>
@@ -5837,6 +6650,1014 @@
       <c r="AN72" s="9" t="n"/>
       <c r="AO72" s="9" t="n"/>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.12142333</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-10.1077</v>
+      </c>
+      <c r="D73" t="n">
+        <v>5038406.6</v>
+      </c>
+      <c r="E73" t="n">
+        <v>47.3366</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.00050694</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.00042156</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00065912</v>
+      </c>
+      <c r="I73" t="n">
+        <v>6</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4457100.45165</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.0253</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.0891</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.8262</v>
+      </c>
+      <c r="P73" t="n">
+        <v>2.7665</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2.6364</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1.8633</v>
+      </c>
+      <c r="U73" t="n">
+        <v>-10.2444</v>
+      </c>
+      <c r="V73" t="n">
+        <v>15.4826</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.12358</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.7762</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3506613.65</v>
+      </c>
+      <c r="E74" t="n">
+        <v>45.3299</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.00046572</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.00038784</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00052447</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>4570943.8205928</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.0515</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8421</v>
+      </c>
+      <c r="P74" t="n">
+        <v>2.0331</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2.0039</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1.1972</v>
+      </c>
+      <c r="U74" t="n">
+        <v>-4.6427</v>
+      </c>
+      <c r="V74" t="n">
+        <v>-23.6538</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.12351333</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.0539</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1939636.43</v>
+      </c>
+      <c r="E75" t="n">
+        <v>45.5439</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.00046416</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.00029271</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00057872</v>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4661927.04178664</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0724</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.8384</v>
+      </c>
+      <c r="P75" t="n">
+        <v>2.2489</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2.1918</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1.1176</v>
+      </c>
+      <c r="U75" t="n">
+        <v>-1.8727</v>
+      </c>
+      <c r="V75" t="n">
+        <v>-22.2936</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.12217667</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.0822</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1486516.37</v>
+      </c>
+      <c r="E76" t="n">
+        <v>50.1889</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.00046766</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.00024573</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00083459</v>
+      </c>
+      <c r="I76" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4457424.7509304</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1.0211</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.0798</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8365</v>
+      </c>
+      <c r="P76" t="n">
+        <v>2.3501</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2.2289</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1.2467</v>
+      </c>
+      <c r="V76" t="n">
+        <v>-15.0515</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.12284333</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="D77" t="n">
+        <v>929365.99</v>
+      </c>
+      <c r="E77" t="n">
+        <v>50.879</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.00022873</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.0001119</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.00032734</v>
+      </c>
+      <c r="I77" t="n">
+        <v>6</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4435028</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.8598</v>
+      </c>
+      <c r="P77" t="n">
+        <v>2.3738</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2.4025</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0.9072</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2.1019</v>
+      </c>
+      <c r="V77" t="n">
+        <v>16.7577</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.12480667</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1.5982</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1990644.43</v>
+      </c>
+      <c r="E78" t="n">
+        <v>49.7013</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.00043651</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.00015964</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00121521</v>
+      </c>
+      <c r="I78" t="n">
+        <v>6</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>4533613.72532</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.0209</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.0764</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.8526</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.4758</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>2.5236</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0.9572000000000001</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.6937</v>
+      </c>
+      <c r="V78" t="n">
+        <v>10.0894</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.10662667</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-14.5665</v>
+      </c>
+      <c r="D79" t="n">
+        <v>10595274.17</v>
+      </c>
+      <c r="E79" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.00043098</v>
+      </c>
+      <c r="G79" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00137298</v>
+      </c>
+      <c r="I79" t="n">
+        <v>6</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>4504548.8596</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1.0106</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.0718</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.8512</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.5298</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>2.6298</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1.3123</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1.7573</v>
+      </c>
+      <c r="V79" t="n">
+        <v>7.6465</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.11481</v>
+      </c>
+      <c r="C80" t="n">
+        <v>7.6747</v>
+      </c>
+      <c r="D80" t="n">
+        <v>16102976.11</v>
+      </c>
+      <c r="E80" t="n">
+        <v>48.7468</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.00032197</v>
+      </c>
+      <c r="G80" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.00065122</v>
+      </c>
+      <c r="I80" t="n">
+        <v>6</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>4074994.672554</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.9143</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="P80" t="n">
+        <v>2.2154</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2.0562</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="U80" t="n">
+        <v>6.2224</v>
+      </c>
+      <c r="V80" t="n">
+        <v>-6.6728</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.11671667</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1.6607</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4824080.91</v>
+      </c>
+      <c r="E81" t="n">
+        <v>48.3761</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.00039177</v>
+      </c>
+      <c r="G81" t="n">
+        <v>7.943e-05</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.00065019</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>4911631.66704</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1.1019</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.1359</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1.8066</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.6371</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.5198</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="U81" t="n">
+        <v>10.1337</v>
+      </c>
+      <c r="V81" t="n">
+        <v>-27.0296</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.11405333</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-2.2819</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3319827.16</v>
+      </c>
+      <c r="E82" t="n">
+        <v>47.9895</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.00034601</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.00023348</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.00045206</v>
+      </c>
+      <c r="I82" t="n">
+        <v>6</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>4449205.14192</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.9982</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.9853</v>
+      </c>
+      <c r="P82" t="n">
+        <v>2.2436</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>2.0276</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="U82" t="n">
+        <v>15.7542</v>
+      </c>
+      <c r="V82" t="n">
+        <v>-11.3131</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.11586333</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1532500.8</v>
+      </c>
+      <c r="E83" t="n">
+        <v>47.6972</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.00048941</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.00020785</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.00095567</v>
+      </c>
+      <c r="I83" t="n">
+        <v>6</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>4145526.81141343</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1.0238</v>
+      </c>
+      <c r="P83" t="n">
+        <v>2.4165</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2.1786</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.8633</v>
+      </c>
+      <c r="U83" t="n">
+        <v>12.099</v>
+      </c>
+      <c r="V83" t="n">
+        <v>9.077400000000001</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.11602</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1110795.35</v>
+      </c>
+      <c r="E84" t="n">
+        <v>46.5952</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.00044605</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.00013606</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.0006569600000000001</v>
+      </c>
+      <c r="I84" t="n">
+        <v>6</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>4047338.16304652</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1.0278</v>
+      </c>
+      <c r="P84" t="n">
+        <v>2.6417</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2.3829</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.9061</v>
+      </c>
+      <c r="U84" t="n">
+        <v>9.456899999999999</v>
+      </c>
+      <c r="V84" t="n">
+        <v>46.225</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.11634667</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1120206.43</v>
+      </c>
+      <c r="E85" t="n">
+        <v>47.8639</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.00032513</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.00014482</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.00044252</v>
+      </c>
+      <c r="I85" t="n">
+        <v>6</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>4040787.76773618</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2.7594</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2.5881</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1.2587</v>
+      </c>
+      <c r="U85" t="n">
+        <v>-1.2991</v>
+      </c>
+      <c r="V85" t="n">
+        <v>22.9898</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.11701667</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="D86" t="n">
+        <v>925636.5600000001</v>
+      </c>
+      <c r="E86" t="n">
+        <v>47.3935</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.00040708</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.00025471</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0005632499999999999</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>WARM</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>3952578.33414</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.8868</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1.0024</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2.7175</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.6166</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1.5983</v>
+      </c>
+      <c r="U86" t="n">
+        <v>-2.0903</v>
+      </c>
+      <c r="V86" t="n">
+        <v>12.456</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:Z1"/>
@@ -5854,7 +7675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6401,6 +8222,138 @@
       <c r="D26" s="8" t="inlineStr">
         <is>
           <t>verdict_pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>08-08</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>funding cool: f_avg 0.000229 vs 0.000466 avg preceding = warming down day</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>fapi funding</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>warmdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CRASH -14.57%, vol 10.6M spike, OI stable 4.5M (crowd flushed but perp size unchanged)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>fapi klines+OI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>flush_wave1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>08-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>REBOUND +7.67%, vol 16.1M (biggest day), OI -9.5% to 4.07M, pos_r 0.851→0.913 (SHORT-COVER partial)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>fapi klines+LSR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>cover_wave1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>08-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pos_r 0.939 leo, OI 4.91M rebuild, div_raw 0.520 CHẠM 0.5 (hedge tháo tạm)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>fapi+LSR</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>hedge_untap_wave1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>08-14</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>pos_r CROSS 1.0 (0.985→1.024), gLSR 2.18 leo, div_raw 0.424 rơi lại (re-hedge)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fapi LSR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>pos_r_cross_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>08-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>INTRADAY PUMP +27.15% (0.11604→0.14754 @13:50 UTC), OI 3.95M→6.27M (+58.8%), vol 24h $44M — cú đẩy operator ghi 18/08</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>fapi ticker+OI intraday</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PUMP_INTRADAY_18</t>
         </is>
       </c>
     </row>
